--- a/research/traditional_assets/database/data/australia/australia_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/australia/australia_brokerage_investment_banking.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ12"/>
+  <dimension ref="A1:AQ10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.2665</v>
+        <v>0.2815</v>
       </c>
       <c r="E2">
-        <v>0.713</v>
+        <v>0.05535</v>
       </c>
       <c r="F2">
-        <v>0.368</v>
+        <v>0.267</v>
       </c>
       <c r="G2">
-        <v>0.04782648674743109</v>
+        <v>0.04059766763848396</v>
       </c>
       <c r="H2">
-        <v>0.04782648674743109</v>
+        <v>0.04059766763848396</v>
       </c>
       <c r="I2">
-        <v>0.0383324521275373</v>
+        <v>0.03064139941690962</v>
       </c>
       <c r="J2">
-        <v>0.03323428876150263</v>
+        <v>0.02411884351409295</v>
       </c>
       <c r="K2">
-        <v>49.307</v>
+        <v>54.37</v>
       </c>
       <c r="L2">
-        <v>0.05667340980667111</v>
+        <v>0.07925655976676385</v>
       </c>
       <c r="M2">
-        <v>57.428</v>
+        <v>56.372</v>
       </c>
       <c r="N2">
-        <v>0.02183383202229463</v>
+        <v>0.02932696559653312</v>
       </c>
       <c r="O2">
-        <v>1.16470278053826</v>
+        <v>1.0368217767151</v>
       </c>
       <c r="P2">
-        <v>47.453</v>
+        <v>44.662</v>
       </c>
       <c r="Q2">
-        <v>0.01804138801549674</v>
+        <v>0.02323495596168953</v>
       </c>
       <c r="R2">
-        <v>0.9623988480337478</v>
+        <v>0.8214456501747286</v>
       </c>
       <c r="S2">
-        <v>9.975</v>
+        <v>11.71</v>
       </c>
       <c r="T2">
-        <v>0.1736957581667479</v>
+        <v>0.2077272404739941</v>
       </c>
       <c r="U2">
-        <v>461.588</v>
+        <v>303.418</v>
       </c>
       <c r="V2">
-        <v>0.1754933979157716</v>
+        <v>0.1578501604940198</v>
       </c>
       <c r="W2">
-        <v>0.1616227310736277</v>
+        <v>0.1449237198657116</v>
       </c>
       <c r="X2">
-        <v>0.03433742764993272</v>
+        <v>0.07082347735009445</v>
       </c>
       <c r="Y2">
-        <v>0.127285303423695</v>
+        <v>0.07410024251561712</v>
       </c>
       <c r="Z2">
-        <v>6.268020143656836</v>
+        <v>1.926906752881231</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.03314724111157188</v>
+        <v>0.0642610485770439</v>
       </c>
       <c r="AC2">
-        <v>-0.03298009575845734</v>
+        <v>-0.0642610485770439</v>
       </c>
       <c r="AD2">
-        <v>288.474</v>
+        <v>293.425</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>288.474</v>
+        <v>293.425</v>
       </c>
       <c r="AG2">
-        <v>-173.114</v>
+        <v>-9.992999999999995</v>
       </c>
       <c r="AH2">
-        <v>0.09883633283813636</v>
+        <v>0.1324350124006201</v>
       </c>
       <c r="AI2">
-        <v>0.2751133931739025</v>
+        <v>0.2759556289117421</v>
       </c>
       <c r="AJ2">
-        <v>-0.07045414217318191</v>
+        <v>-0.005225925989843094</v>
       </c>
       <c r="AK2">
-        <v>-0.2949251758163878</v>
+        <v>-0.01315063950297873</v>
       </c>
       <c r="AL2">
-        <v>5.833</v>
+        <v>3.42</v>
       </c>
       <c r="AM2">
-        <v>5.805000000000001</v>
+        <v>3.415</v>
       </c>
       <c r="AN2">
-        <v>6.932804614275415</v>
+        <v>10.53590664272891</v>
       </c>
       <c r="AO2">
-        <v>5.717469569689697</v>
+        <v>6.146198830409357</v>
       </c>
       <c r="AP2">
-        <v>-4.160394136024995</v>
+        <v>-0.358815080789946</v>
       </c>
       <c r="AQ2">
-        <v>5.74504737295435</v>
+        <v>6.155197657393852</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sequoia Financial Group Limited (ASX:SEQ)</t>
+          <t>COG Financial Services Limited (ASX:COG)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -725,46 +725,43 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.383</v>
-      </c>
-      <c r="E3">
-        <v>0.769</v>
+        <v>0.314</v>
       </c>
       <c r="G3">
-        <v>0.09186712485681557</v>
+        <v>0.1601085481682497</v>
       </c>
       <c r="H3">
-        <v>0.09186712485681557</v>
+        <v>0.1601085481682497</v>
       </c>
       <c r="I3">
-        <v>0.07216494845360824</v>
+        <v>0.1293532338308458</v>
       </c>
       <c r="J3">
-        <v>0.04929494015878658</v>
+        <v>0.09534350718318522</v>
       </c>
       <c r="K3">
-        <v>4.16</v>
+        <v>13.6</v>
       </c>
       <c r="L3">
-        <v>0.04765177548682704</v>
+        <v>0.06151062867480778</v>
       </c>
       <c r="M3">
-        <v>0.543</v>
+        <v>11.4</v>
       </c>
       <c r="N3">
-        <v>0.008302752293577981</v>
+        <v>0.06067056945183608</v>
       </c>
       <c r="O3">
-        <v>0.1305288461538462</v>
+        <v>0.8382352941176471</v>
       </c>
       <c r="P3">
-        <v>0.543</v>
+        <v>11.4</v>
       </c>
       <c r="Q3">
-        <v>0.008302752293577981</v>
+        <v>0.06067056945183608</v>
       </c>
       <c r="R3">
-        <v>0.1305288461538462</v>
+        <v>0.8382352941176471</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -773,73 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>26</v>
+        <v>52.4</v>
       </c>
       <c r="V3">
-        <v>0.3975535168195719</v>
+        <v>0.2788717402873869</v>
       </c>
       <c r="W3">
-        <v>0.1816593886462882</v>
+        <v>0.1190893169877408</v>
       </c>
       <c r="X3">
-        <v>0.03374448387197769</v>
+        <v>0.08264416459530387</v>
       </c>
       <c r="Y3">
-        <v>0.1479149047743105</v>
+        <v>0.03644515239243694</v>
       </c>
       <c r="Z3">
-        <v>34.92000000000004</v>
+        <v>1.462301587301587</v>
       </c>
       <c r="AA3">
-        <v>1.72137931034483</v>
+        <v>0.139420961892872</v>
       </c>
       <c r="AB3">
-        <v>0.03311116360805268</v>
+        <v>0.05929134888173726</v>
       </c>
       <c r="AC3">
-        <v>1.688268146736777</v>
+        <v>0.08012961301113475</v>
       </c>
       <c r="AD3">
-        <v>2.47</v>
+        <v>167.6</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>2.47</v>
+        <v>167.6</v>
       </c>
       <c r="AG3">
-        <v>-23.53</v>
+        <v>115.2</v>
       </c>
       <c r="AH3">
-        <v>0.03639310446441727</v>
+        <v>0.4714486638537271</v>
       </c>
       <c r="AI3">
-        <v>0.07424105801021942</v>
+        <v>0.5396007726980038</v>
       </c>
       <c r="AJ3">
-        <v>-0.5619775495581562</v>
+        <v>0.3800725833058396</v>
       </c>
       <c r="AK3">
-        <v>-3.236588720770289</v>
+        <v>0.4461657629744384</v>
       </c>
       <c r="AL3">
-        <v>0.173</v>
+        <v>3.42</v>
       </c>
       <c r="AM3">
-        <v>0.161</v>
+        <v>3.42</v>
       </c>
       <c r="AN3">
-        <v>0.3079800498753117</v>
+        <v>4.734463276836158</v>
       </c>
       <c r="AO3">
-        <v>36.41618497109827</v>
+        <v>8.362573099415206</v>
       </c>
       <c r="AP3">
-        <v>-2.933915211970075</v>
+        <v>3.254237288135593</v>
       </c>
       <c r="AQ3">
-        <v>39.1304347826087</v>
+        <v>8.362573099415206</v>
       </c>
     </row>
     <row r="4">
@@ -850,7 +847,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>COG Financial Services Limited (ASX:COG)</t>
+          <t>Finexia Financial Group Limited (ASX:FNX)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -859,118 +856,103 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.7559999999999999</v>
+        <v>0.313</v>
       </c>
       <c r="G4">
-        <v>0.1821305841924399</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>0.1821305841924399</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>0.1502209131075111</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>0.1502209131075111</v>
+        <v>0</v>
       </c>
       <c r="K4">
-        <v>-19.8</v>
+        <v>2.27</v>
       </c>
       <c r="L4">
-        <v>-0.0972017673048601</v>
+        <v>0.3961605584642234</v>
       </c>
       <c r="M4">
-        <v>3.3</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.01622418879056047</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>-0.1666666666666667</v>
+        <v>-0</v>
       </c>
       <c r="P4">
-        <v>3.3</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.01622418879056047</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>-0.1666666666666667</v>
+        <v>-0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
       <c r="U4">
-        <v>70.90000000000001</v>
+        <v>1.87</v>
       </c>
       <c r="V4">
-        <v>0.3485742379547689</v>
+        <v>0.2586445366528354</v>
       </c>
       <c r="W4">
-        <v>-0.1645885286783043</v>
+        <v>0.58656330749354</v>
       </c>
       <c r="X4">
-        <v>0.04385384210341248</v>
+        <v>0.1405311141478158</v>
       </c>
       <c r="Y4">
-        <v>-0.2084423707817167</v>
+        <v>0.4460321933457242</v>
       </c>
       <c r="Z4">
-        <v>2.32004555808656</v>
+        <v>0.3911262798634813</v>
       </c>
       <c r="AA4">
-        <v>0.3485193621867881</v>
+        <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.03282144579308181</v>
+        <v>0.05908847209848473</v>
       </c>
       <c r="AC4">
-        <v>0.3156979163937063</v>
+        <v>-0.05908847209848473</v>
       </c>
       <c r="AD4">
-        <v>169.4</v>
+        <v>28.6</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>169.4</v>
+        <v>28.6</v>
       </c>
       <c r="AG4">
-        <v>98.5</v>
+        <v>26.73</v>
       </c>
       <c r="AH4">
-        <v>0.4543991416309013</v>
+        <v>0.7982137873290539</v>
       </c>
       <c r="AI4">
-        <v>0.5436456996148908</v>
+        <v>0.8244450850389162</v>
       </c>
       <c r="AJ4">
-        <v>0.3262669758198079</v>
+        <v>0.7871024734982333</v>
       </c>
       <c r="AK4">
-        <v>0.4092230992937266</v>
+        <v>0.8144424131627057</v>
       </c>
       <c r="AL4">
-        <v>5.66</v>
+        <v>0</v>
       </c>
       <c r="AM4">
-        <v>5.66</v>
-      </c>
-      <c r="AN4">
-        <v>4.566037735849057</v>
-      </c>
-      <c r="AO4">
-        <v>5.406360424028269</v>
-      </c>
-      <c r="AP4">
-        <v>2.654986522911051</v>
-      </c>
-      <c r="AQ4">
-        <v>5.406360424028269</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -981,7 +963,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>E&amp;P Financial Group Limited (ASX:EP1)</t>
+          <t>Sequoia Financial Group Limited (ASX:SEQ)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -990,7 +972,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.026</v>
+        <v>0.446</v>
+      </c>
+      <c r="E5">
+        <v>0.524</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1005,91 +990,94 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>-14.1</v>
+        <v>4.73</v>
       </c>
       <c r="L5">
-        <v>-0.09591836734693877</v>
+        <v>0.05320584926884139</v>
       </c>
       <c r="M5">
-        <v>3.71</v>
+        <v>0.757</v>
       </c>
       <c r="N5">
-        <v>0.0361598440545809</v>
+        <v>0.01399260628465804</v>
       </c>
       <c r="O5">
-        <v>-0.2631205673758865</v>
+        <v>0.1600422832980972</v>
       </c>
       <c r="P5">
-        <v>3.46</v>
+        <v>0.757</v>
       </c>
       <c r="Q5">
-        <v>0.03372319688109162</v>
+        <v>0.01399260628465804</v>
       </c>
       <c r="R5">
-        <v>-0.2453900709219858</v>
+        <v>0.1600422832980972</v>
       </c>
       <c r="S5">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="T5">
-        <v>0.0673854447439353</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>38.1</v>
+        <v>26</v>
       </c>
       <c r="V5">
-        <v>0.3713450292397661</v>
+        <v>0.4805914972273567</v>
       </c>
       <c r="W5">
-        <v>-0.1147274206672091</v>
+        <v>0.1707581227436823</v>
       </c>
       <c r="X5">
-        <v>0.03635007080351529</v>
+        <v>0.07137928191446533</v>
       </c>
       <c r="Y5">
-        <v>-0.1510774914707244</v>
+        <v>0.099378840829217</v>
       </c>
       <c r="Z5">
-        <v>2.118155619596541</v>
+        <v>3.445736434108528</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.0324426667351376</v>
+        <v>0.06264449574283272</v>
       </c>
       <c r="AC5">
-        <v>-0.0324426667351376</v>
+        <v>-0.06264449574283272</v>
       </c>
       <c r="AD5">
-        <v>24.9</v>
+        <v>16</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>24.9</v>
+        <v>16</v>
       </c>
       <c r="AG5">
-        <v>-13.2</v>
+        <v>-10</v>
       </c>
       <c r="AH5">
-        <v>0.1952941176470588</v>
+        <v>0.2282453637660485</v>
       </c>
       <c r="AI5">
-        <v>0.1738826815642458</v>
+        <v>0.3361344537815126</v>
       </c>
       <c r="AJ5">
-        <v>-0.1476510067114094</v>
+        <v>-0.2267573696145125</v>
       </c>
       <c r="AK5">
-        <v>-0.1255946717411989</v>
+        <v>-0.4629629629629629</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>0</v>
+        <v>-0.005</v>
+      </c>
+      <c r="AQ5">
+        <v>-0</v>
       </c>
     </row>
     <row r="6">
@@ -1100,7 +1088,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Finexia Financial Group Limited (ASX:FNX)</t>
+          <t>E&amp;P Financial Group Limited (ASX:EP1)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1109,7 +1097,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.255</v>
+        <v>-0.0134</v>
+      </c>
+      <c r="E6">
+        <v>-0.187</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1124,82 +1115,85 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>0.951</v>
+        <v>4.35</v>
       </c>
       <c r="L6">
-        <v>0.2788856304985337</v>
+        <v>0.03082919914953933</v>
       </c>
       <c r="M6">
-        <v>-0</v>
+        <v>7.094999999999999</v>
       </c>
       <c r="N6">
-        <v>-0</v>
+        <v>0.08969658659924146</v>
       </c>
       <c r="O6">
-        <v>-0</v>
+        <v>1.631034482758621</v>
       </c>
       <c r="P6">
-        <v>-0</v>
+        <v>4.274999999999999</v>
       </c>
       <c r="Q6">
-        <v>-0</v>
+        <v>0.05404551201011377</v>
       </c>
       <c r="R6">
-        <v>-0</v>
+        <v>0.9827586206896551</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>2.819999999999999</v>
+      </c>
+      <c r="T6">
+        <v>0.3974630021141649</v>
       </c>
       <c r="U6">
-        <v>1.1</v>
+        <v>51.1</v>
       </c>
       <c r="V6">
-        <v>0.1639344262295082</v>
+        <v>0.6460176991150444</v>
       </c>
       <c r="W6">
-        <v>0.3850202429149797</v>
+        <v>0.036770921386306</v>
       </c>
       <c r="X6">
-        <v>0.05770888248168478</v>
+        <v>0.0756086412957668</v>
       </c>
       <c r="Y6">
-        <v>0.327311360433295</v>
+        <v>-0.0388377199094608</v>
       </c>
       <c r="Z6">
-        <v>1.154366960054164</v>
+        <v>2.528673835125448</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.03262319947866281</v>
+        <v>0.06382961336518431</v>
       </c>
       <c r="AC6">
-        <v>-0.03262319947866281</v>
+        <v>-0.06382961336518431</v>
       </c>
       <c r="AD6">
-        <v>12.9</v>
+        <v>41.1</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>12.9</v>
+        <v>41.1</v>
       </c>
       <c r="AG6">
-        <v>11.8</v>
+        <v>-10</v>
       </c>
       <c r="AH6">
-        <v>0.6578276389597145</v>
+        <v>0.3419301164725458</v>
       </c>
       <c r="AI6">
-        <v>0.7692307692307693</v>
+        <v>0.2674040338321406</v>
       </c>
       <c r="AJ6">
-        <v>0.637493246893571</v>
+        <v>-0.1447178002894356</v>
       </c>
       <c r="AK6">
-        <v>0.7530312699425654</v>
+        <v>-0.09746588693957116</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1216,7 +1210,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bell Financial Group Limited (ASX:BFG)</t>
+          <t>BIR Financial Limited (ASX:BIR)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1225,10 +1219,7 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.112</v>
-      </c>
-      <c r="E7">
-        <v>0.244</v>
+        <v>1.393</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1243,85 +1234,82 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>35.4</v>
+        <v>-2.14</v>
       </c>
       <c r="L7">
-        <v>0.1590296495956873</v>
+        <v>-1.086294416243655</v>
       </c>
       <c r="M7">
-        <v>25.205</v>
+        <v>-0</v>
       </c>
       <c r="N7">
-        <v>0.05794252873563218</v>
+        <v>-0</v>
       </c>
       <c r="O7">
-        <v>0.7120056497175141</v>
+        <v>0</v>
       </c>
       <c r="P7">
-        <v>25.2</v>
+        <v>-0</v>
       </c>
       <c r="Q7">
-        <v>0.05793103448275862</v>
+        <v>-0</v>
       </c>
       <c r="R7">
-        <v>0.711864406779661</v>
+        <v>0</v>
       </c>
       <c r="S7">
-        <v>0.004999999999999005</v>
-      </c>
-      <c r="T7">
-        <v>0.0001983733386232496</v>
+        <v>0</v>
       </c>
       <c r="U7">
-        <v>185.7</v>
+        <v>0.048</v>
       </c>
       <c r="V7">
-        <v>0.4268965517241379</v>
+        <v>0.006611570247933885</v>
       </c>
       <c r="W7">
-        <v>0.2403258655804481</v>
+        <v>1.289156626506024</v>
       </c>
       <c r="X7">
-        <v>0.03493037142788774</v>
+        <v>0.07026767278572359</v>
       </c>
       <c r="Y7">
-        <v>0.2053954941525603</v>
+        <v>1.2188889537203</v>
       </c>
       <c r="Z7">
-        <v>-2.306735751295337</v>
+        <v>5.02551020408163</v>
       </c>
       <c r="AA7">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.03277687290182359</v>
+        <v>0.06469248378890348</v>
       </c>
       <c r="AC7">
-        <v>-0.03277687290182359</v>
+        <v>-0.06469248378890348</v>
       </c>
       <c r="AD7">
-        <v>57</v>
+        <v>1.72</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>57</v>
+        <v>1.72</v>
       </c>
       <c r="AG7">
-        <v>-128.7</v>
+        <v>1.672</v>
       </c>
       <c r="AH7">
-        <v>0.1158536585365854</v>
+        <v>0.1915367483296214</v>
       </c>
       <c r="AI7">
-        <v>0.2507699076110866</v>
+        <v>-4.410256410256411</v>
       </c>
       <c r="AJ7">
-        <v>-0.4201762977473065</v>
+        <v>0.187192118226601</v>
       </c>
       <c r="AK7">
-        <v>-3.093749999999998</v>
+        <v>-3.817351598173516</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1347,10 +1335,10 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.278</v>
+        <v>0.17</v>
       </c>
       <c r="E8">
-        <v>0.713</v>
+        <v>0.16</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1365,85 +1353,85 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>39.4</v>
+        <v>28.1</v>
       </c>
       <c r="L8">
-        <v>0.4008138351983723</v>
+        <v>0.3435207823960881</v>
       </c>
       <c r="M8">
-        <v>16.96</v>
+        <v>23.49</v>
       </c>
       <c r="N8">
-        <v>0.0717124735729387</v>
+        <v>0.1967336683417085</v>
       </c>
       <c r="O8">
-        <v>0.4304568527918782</v>
+        <v>0.8359430604982205</v>
       </c>
       <c r="P8">
-        <v>11</v>
+        <v>21.5</v>
       </c>
       <c r="Q8">
-        <v>0.04651162790697674</v>
+        <v>0.1800670016750419</v>
       </c>
       <c r="R8">
-        <v>0.2791878172588833</v>
+        <v>0.7651245551601423</v>
       </c>
       <c r="S8">
-        <v>5.960000000000001</v>
+        <v>1.989999999999998</v>
       </c>
       <c r="T8">
-        <v>0.3514150943396226</v>
+        <v>0.08471690080885477</v>
       </c>
       <c r="U8">
-        <v>72</v>
+        <v>131.4</v>
       </c>
       <c r="V8">
-        <v>0.3044397463002114</v>
+        <v>1.100502512562814</v>
       </c>
       <c r="W8">
-        <v>0.4993662864385297</v>
+        <v>0.2190179267342167</v>
       </c>
       <c r="X8">
-        <v>0.03351373055732267</v>
+        <v>0.06632626613547396</v>
       </c>
       <c r="Y8">
-        <v>0.4658525558812071</v>
+        <v>0.1526916605987427</v>
       </c>
       <c r="Z8">
-        <v>2.056485355648535</v>
+        <v>1.671434409480997</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.03318331861509109</v>
+        <v>0.065560239261896</v>
       </c>
       <c r="AC8">
-        <v>-0.03318331861509109</v>
+        <v>-0.065560239261896</v>
       </c>
       <c r="AD8">
-        <v>4.64</v>
+        <v>3.38</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>4.64</v>
+        <v>3.38</v>
       </c>
       <c r="AG8">
-        <v>-67.36</v>
+        <v>-128.02</v>
       </c>
       <c r="AH8">
-        <v>0.01924193414613917</v>
+        <v>0.02752891350382798</v>
       </c>
       <c r="AI8">
-        <v>0.03490296374304197</v>
+        <v>0.02476553341148886</v>
       </c>
       <c r="AJ8">
-        <v>-0.3982499704386899</v>
+        <v>14.85150812064965</v>
       </c>
       <c r="AK8">
-        <v>-1.105349524122087</v>
+        <v>-25.20078740157489</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1469,10 +1457,13 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.201</v>
+        <v>0.25</v>
+      </c>
+      <c r="E9">
+        <v>-0.0493</v>
       </c>
       <c r="F9">
-        <v>0.368</v>
+        <v>0.267</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1487,85 +1478,85 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>7.32</v>
+        <v>10.1</v>
       </c>
       <c r="L9">
-        <v>0.08948655256723717</v>
+        <v>0.07645722937168811</v>
       </c>
       <c r="M9">
-        <v>7.71</v>
+        <v>13.63</v>
       </c>
       <c r="N9">
-        <v>0.005477019251260922</v>
+        <v>0.009457396613932833</v>
       </c>
       <c r="O9">
-        <v>1.05327868852459</v>
+        <v>1.34950495049505</v>
       </c>
       <c r="P9">
-        <v>3.95</v>
+        <v>6.73</v>
       </c>
       <c r="Q9">
-        <v>0.002805995595652483</v>
+        <v>0.004669719678046073</v>
       </c>
       <c r="R9">
-        <v>0.5396174863387978</v>
+        <v>0.6663366336633664</v>
       </c>
       <c r="S9">
-        <v>3.76</v>
+        <v>6.9</v>
       </c>
       <c r="T9">
-        <v>0.4876783398184176</v>
+        <v>0.5062362435803375</v>
       </c>
       <c r="U9">
-        <v>47.6</v>
+        <v>29.9</v>
       </c>
       <c r="V9">
-        <v>0.03381402287419195</v>
+        <v>0.0207466000555093</v>
       </c>
       <c r="W9">
-        <v>0.1415860735009671</v>
+        <v>0.07437407952871869</v>
       </c>
       <c r="X9">
-        <v>0.0333943368392865</v>
+        <v>0.06623845879236283</v>
       </c>
       <c r="Y9">
-        <v>0.1081917366616806</v>
+        <v>0.008135620736355861</v>
       </c>
       <c r="Z9">
-        <v>3.843984962406015</v>
+        <v>2.410583941605838</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.03325440154812175</v>
+        <v>0.06559731363895703</v>
       </c>
       <c r="AC9">
-        <v>-0.03325440154812175</v>
+        <v>-0.06559731363895703</v>
       </c>
       <c r="AD9">
-        <v>14.4</v>
+        <v>34.1</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>14.4</v>
+        <v>34.1</v>
       </c>
       <c r="AG9">
-        <v>-33.2</v>
+        <v>4.200000000000003</v>
       </c>
       <c r="AH9">
-        <v>0.01012587019196962</v>
+        <v>0.02311394292686234</v>
       </c>
       <c r="AI9">
-        <v>0.09587217043941411</v>
+        <v>0.09798850574712645</v>
       </c>
       <c r="AJ9">
-        <v>-0.02415423790469262</v>
+        <v>0.002905770029057702</v>
       </c>
       <c r="AK9">
-        <v>-0.3235867446393762</v>
+        <v>0.01320339515875512</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1582,7 +1573,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SelfWealth Limited (ASX:SWF)</t>
+          <t>Raiz Invest Limited (ASX:RZI)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1591,25 +1582,25 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.88</v>
+        <v>0.188</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>-0.5676691729323308</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>-0.5676691729323308</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>-0.5699248120300752</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>-0.5699248120300752</v>
       </c>
       <c r="K10">
-        <v>-0.485</v>
+        <v>-6.64</v>
       </c>
       <c r="L10">
-        <v>-0.03514492753623188</v>
+        <v>-0.4992481203007518</v>
       </c>
       <c r="M10">
         <v>-0</v>
@@ -1633,296 +1624,67 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>5.64</v>
+        <v>10.7</v>
       </c>
       <c r="V10">
-        <v>0.1112426035502958</v>
+        <v>0.4115384615384615</v>
       </c>
       <c r="W10">
-        <v>-0.1823308270676691</v>
+        <v>-0.2313588850174216</v>
       </c>
       <c r="X10">
-        <v>0.03327304707520042</v>
+        <v>0.06646360115533642</v>
       </c>
       <c r="Y10">
-        <v>-0.2156038741428696</v>
+        <v>-0.297822486172758</v>
       </c>
       <c r="Z10">
-        <v>-15.97222222222222</v>
+        <v>3.002935199819373</v>
       </c>
       <c r="AA10">
-        <v>-0</v>
+        <v>-1.711447279295553</v>
       </c>
       <c r="AB10">
-        <v>0.03326359718419037</v>
+        <v>0.0655029203357009</v>
       </c>
       <c r="AC10">
-        <v>-0.03326359718419037</v>
+        <v>-1.776950199631254</v>
       </c>
       <c r="AD10">
-        <v>0.035</v>
+        <v>0.925</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>0.035</v>
+        <v>0.925</v>
       </c>
       <c r="AG10">
-        <v>-5.605</v>
+        <v>-9.774999999999999</v>
       </c>
       <c r="AH10">
-        <v>0.0006898590716467923</v>
+        <v>0.03435468895078923</v>
       </c>
       <c r="AI10">
-        <v>0.008111239860950173</v>
+        <v>0.02835249042145594</v>
       </c>
       <c r="AJ10">
-        <v>-0.1242931588867945</v>
+        <v>-0.6024653312788905</v>
       </c>
       <c r="AK10">
-        <v>4.230188679245285</v>
+        <v>-0.4458380843785632</v>
       </c>
       <c r="AL10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>-0.016</v>
-      </c>
-      <c r="AQ10">
-        <v>-0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>BIR Financial Limited (ASX:BIR)</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Brokerage &amp; Investment Banking</t>
-        </is>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>-0.899</v>
-      </c>
-      <c r="L11">
-        <v>-0.5583850931677018</v>
-      </c>
-      <c r="M11">
-        <v>-0</v>
-      </c>
-      <c r="N11">
-        <v>-0</v>
-      </c>
-      <c r="O11">
-        <v>0</v>
-      </c>
-      <c r="P11">
-        <v>-0</v>
-      </c>
-      <c r="Q11">
-        <v>-0</v>
-      </c>
-      <c r="R11">
-        <v>0</v>
-      </c>
-      <c r="S11">
-        <v>0</v>
-      </c>
-      <c r="U11">
-        <v>0.148</v>
-      </c>
-      <c r="V11">
-        <v>0.09135802469135801</v>
-      </c>
-      <c r="W11">
-        <v>1.287965616045845</v>
-      </c>
-      <c r="X11">
-        <v>0.05053153797781273</v>
-      </c>
-      <c r="Y11">
-        <v>1.237434078068033</v>
-      </c>
-      <c r="Z11">
-        <v>2.36417033773862</v>
-      </c>
-      <c r="AA11">
-        <v>0</v>
-      </c>
-      <c r="AB11">
-        <v>0.03393128400790527</v>
-      </c>
-      <c r="AC11">
-        <v>-0.03393128400790527</v>
-      </c>
-      <c r="AD11">
-        <v>2.2</v>
-      </c>
-      <c r="AE11">
-        <v>0</v>
-      </c>
-      <c r="AF11">
-        <v>2.2</v>
-      </c>
-      <c r="AG11">
-        <v>2.052</v>
-      </c>
-      <c r="AH11">
-        <v>0.5759162303664922</v>
-      </c>
-      <c r="AI11">
-        <v>4.074074074074073</v>
-      </c>
-      <c r="AJ11">
-        <v>0.5588235294117647</v>
-      </c>
-      <c r="AK11">
-        <v>5.234693877551019</v>
-      </c>
-      <c r="AL11">
-        <v>0</v>
-      </c>
-      <c r="AM11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Raiz Invest Limited (ASX:RZI)</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Brokerage &amp; Investment Banking</t>
-        </is>
-      </c>
-      <c r="G12">
-        <v>-0.3342857142857142</v>
-      </c>
-      <c r="H12">
-        <v>-0.3342857142857142</v>
-      </c>
-      <c r="I12">
-        <v>-0.3380952380952381</v>
-      </c>
-      <c r="J12">
-        <v>-0.3380952380952381</v>
-      </c>
-      <c r="K12">
-        <v>-2.64</v>
-      </c>
-      <c r="L12">
-        <v>-0.2514285714285714</v>
-      </c>
-      <c r="M12">
-        <v>-0</v>
-      </c>
-      <c r="N12">
-        <v>-0</v>
-      </c>
-      <c r="O12">
-        <v>0</v>
-      </c>
-      <c r="P12">
-        <v>-0</v>
-      </c>
-      <c r="Q12">
-        <v>-0</v>
-      </c>
-      <c r="R12">
-        <v>0</v>
-      </c>
-      <c r="S12">
-        <v>0</v>
-      </c>
-      <c r="U12">
-        <v>14.4</v>
-      </c>
-      <c r="V12">
-        <v>0.1194029850746269</v>
-      </c>
-      <c r="W12">
-        <v>-0.1216589861751152</v>
-      </c>
-      <c r="X12">
-        <v>0.03332004251262828</v>
-      </c>
-      <c r="Y12">
-        <v>-0.1549790286877435</v>
-      </c>
-      <c r="Z12">
-        <v>2.798507462686568</v>
-      </c>
-      <c r="AA12">
-        <v>-0.9461620469083158</v>
-      </c>
-      <c r="AB12">
-        <v>0.03326001347696902</v>
-      </c>
-      <c r="AC12">
-        <v>-0.9794220603852849</v>
-      </c>
-      <c r="AD12">
-        <v>0.529</v>
-      </c>
-      <c r="AE12">
-        <v>0</v>
-      </c>
-      <c r="AF12">
-        <v>0.529</v>
-      </c>
-      <c r="AG12">
-        <v>-13.871</v>
-      </c>
-      <c r="AH12">
-        <v>0.004367244838147761</v>
-      </c>
-      <c r="AI12">
-        <v>0.01860775968201485</v>
-      </c>
-      <c r="AJ12">
-        <v>-0.1299646768919413</v>
-      </c>
-      <c r="AK12">
-        <v>-0.9887376149404806</v>
-      </c>
-      <c r="AL12">
-        <v>0</v>
-      </c>
-      <c r="AM12">
-        <v>0</v>
-      </c>
-      <c r="AN12">
-        <v>-0.1507122507122507</v>
-      </c>
-      <c r="AP12">
-        <v>3.951851851851852</v>
+        <v>0</v>
+      </c>
+      <c r="AN10">
+        <v>-0.1225165562913907</v>
+      </c>
+      <c r="AP10">
+        <v>1.294701986754967</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/australia/australia_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/australia/australia_brokerage_investment_banking.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ10"/>
+  <dimension ref="A1:AQ9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.2815</v>
+        <v>0.309</v>
       </c>
       <c r="E2">
-        <v>0.05535</v>
+        <v>0.389</v>
       </c>
       <c r="F2">
-        <v>0.267</v>
+        <v>0.179</v>
       </c>
       <c r="G2">
-        <v>0.04059766763848396</v>
+        <v>0.06016956337431115</v>
       </c>
       <c r="H2">
-        <v>0.04059766763848396</v>
+        <v>0.05844849512505298</v>
       </c>
       <c r="I2">
-        <v>0.03064139941690962</v>
+        <v>0.04498516320474778</v>
       </c>
       <c r="J2">
-        <v>0.02411884351409295</v>
+        <v>0.03965481053687256</v>
       </c>
       <c r="K2">
-        <v>54.37</v>
+        <v>13.751</v>
       </c>
       <c r="L2">
-        <v>0.07925655976676385</v>
+        <v>0.02331665960152607</v>
       </c>
       <c r="M2">
-        <v>56.372</v>
+        <v>36.4282</v>
       </c>
       <c r="N2">
-        <v>0.02932696559653312</v>
+        <v>0.01565027237889021</v>
       </c>
       <c r="O2">
-        <v>1.0368217767151</v>
+        <v>2.649130972292924</v>
       </c>
       <c r="P2">
-        <v>44.662</v>
+        <v>29.6992</v>
       </c>
       <c r="Q2">
-        <v>0.02323495596168953</v>
+        <v>0.01275936141327697</v>
       </c>
       <c r="R2">
-        <v>0.8214456501747286</v>
+        <v>2.159784742927787</v>
       </c>
       <c r="S2">
-        <v>11.71</v>
+        <v>6.728999999999998</v>
       </c>
       <c r="T2">
-        <v>0.2077272404739941</v>
+        <v>0.184719530473644</v>
       </c>
       <c r="U2">
-        <v>303.418</v>
+        <v>178.38</v>
       </c>
       <c r="V2">
-        <v>0.1578501604940198</v>
+        <v>0.07663556220034026</v>
       </c>
       <c r="W2">
-        <v>0.1449237198657116</v>
+        <v>0.008036890645586298</v>
       </c>
       <c r="X2">
-        <v>0.07082347735009445</v>
+        <v>0.05681560057097103</v>
       </c>
       <c r="Y2">
-        <v>0.07410024251561712</v>
+        <v>-0.04877870992538473</v>
       </c>
       <c r="Z2">
-        <v>1.926906752881231</v>
+        <v>1.381121665167866</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.0642610485770439</v>
+        <v>0.05646858426785069</v>
       </c>
       <c r="AC2">
-        <v>-0.0642610485770439</v>
+        <v>-0.05649485895884847</v>
       </c>
       <c r="AD2">
-        <v>293.425</v>
+        <v>275.238</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>293.425</v>
+        <v>275.238</v>
       </c>
       <c r="AG2">
-        <v>-9.992999999999995</v>
+        <v>96.858</v>
       </c>
       <c r="AH2">
-        <v>0.1324350124006201</v>
+        <v>0.1057437190678933</v>
       </c>
       <c r="AI2">
-        <v>0.2759556289117421</v>
+        <v>0.3026529054846067</v>
       </c>
       <c r="AJ2">
-        <v>-0.005225925989843094</v>
+        <v>0.03994971330147519</v>
       </c>
       <c r="AK2">
-        <v>-0.01315063950297873</v>
+        <v>0.1324937964921112</v>
       </c>
       <c r="AL2">
-        <v>3.42</v>
+        <v>5.65</v>
       </c>
       <c r="AM2">
-        <v>3.415</v>
+        <v>5.479</v>
       </c>
       <c r="AN2">
-        <v>10.53590664272891</v>
+        <v>7.984856396866841</v>
       </c>
       <c r="AO2">
-        <v>6.146198830409357</v>
+        <v>4.695575221238938</v>
       </c>
       <c r="AP2">
-        <v>-0.358815080789946</v>
+        <v>2.809921671018277</v>
       </c>
       <c r="AQ2">
-        <v>6.155197657393852</v>
+        <v>4.84212447526921</v>
       </c>
     </row>
     <row r="3">
@@ -725,43 +725,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.314</v>
+        <v>0.173</v>
+      </c>
+      <c r="E3">
+        <v>0.16</v>
       </c>
       <c r="G3">
-        <v>0.1601085481682497</v>
+        <v>0.1629720853858785</v>
       </c>
       <c r="H3">
-        <v>0.1601085481682497</v>
+        <v>0.1629720853858785</v>
       </c>
       <c r="I3">
-        <v>0.1293532338308458</v>
+        <v>0.1305418719211823</v>
       </c>
       <c r="J3">
-        <v>0.09534350718318522</v>
+        <v>0.08363056821474672</v>
       </c>
       <c r="K3">
-        <v>13.6</v>
+        <v>5.36</v>
       </c>
       <c r="L3">
-        <v>0.06151062867480778</v>
+        <v>0.02200328407224959</v>
       </c>
       <c r="M3">
-        <v>11.4</v>
+        <v>10.7</v>
       </c>
       <c r="N3">
-        <v>0.06067056945183608</v>
+        <v>0.05728051391862955</v>
       </c>
       <c r="O3">
-        <v>0.8382352941176471</v>
+        <v>1.996268656716418</v>
       </c>
       <c r="P3">
-        <v>11.4</v>
+        <v>10.7</v>
       </c>
       <c r="Q3">
-        <v>0.06067056945183608</v>
+        <v>0.05728051391862955</v>
       </c>
       <c r="R3">
-        <v>0.8382352941176471</v>
+        <v>1.996268656716418</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +773,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>52.4</v>
+        <v>67.8</v>
       </c>
       <c r="V3">
-        <v>0.2788717402873869</v>
+        <v>0.3629550321199143</v>
       </c>
       <c r="W3">
-        <v>0.1190893169877408</v>
+        <v>0.04550084889643464</v>
       </c>
       <c r="X3">
-        <v>0.08264416459530387</v>
+        <v>0.06920762067611937</v>
       </c>
       <c r="Y3">
-        <v>0.03644515239243694</v>
+        <v>-0.02370677177968473</v>
       </c>
       <c r="Z3">
-        <v>1.462301587301587</v>
+        <v>1.500924214417745</v>
       </c>
       <c r="AA3">
-        <v>0.139420961892872</v>
+        <v>0.1255231448990284</v>
       </c>
       <c r="AB3">
-        <v>0.05929134888173726</v>
+        <v>0.05026854745021059</v>
       </c>
       <c r="AC3">
-        <v>0.08012961301113475</v>
+        <v>0.07525459744881777</v>
       </c>
       <c r="AD3">
-        <v>167.6</v>
+        <v>188.8</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>167.6</v>
+        <v>188.8</v>
       </c>
       <c r="AG3">
-        <v>115.2</v>
+        <v>121</v>
       </c>
       <c r="AH3">
-        <v>0.4714486638537271</v>
+        <v>0.5026624068157615</v>
       </c>
       <c r="AI3">
-        <v>0.5396007726980038</v>
+        <v>0.5695324283559579</v>
       </c>
       <c r="AJ3">
-        <v>0.3800725833058396</v>
+        <v>0.3931124106562703</v>
       </c>
       <c r="AK3">
-        <v>0.4461657629744384</v>
+        <v>0.4588547591960562</v>
       </c>
       <c r="AL3">
-        <v>3.42</v>
+        <v>5.65</v>
       </c>
       <c r="AM3">
-        <v>3.42</v>
+        <v>5.65</v>
       </c>
       <c r="AN3">
-        <v>4.734463276836158</v>
+        <v>4.755667506297229</v>
       </c>
       <c r="AO3">
-        <v>8.362573099415206</v>
+        <v>5.628318584070796</v>
       </c>
       <c r="AP3">
-        <v>3.254237288135593</v>
+        <v>3.047858942065491</v>
       </c>
       <c r="AQ3">
-        <v>8.362573099415206</v>
+        <v>5.628318584070796</v>
       </c>
     </row>
     <row r="4">
@@ -856,7 +859,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.313</v>
+        <v>0.35</v>
+      </c>
+      <c r="E4">
+        <v>0.716</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -871,82 +877,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>2.27</v>
+        <v>2.14</v>
       </c>
       <c r="L4">
-        <v>0.3961605584642234</v>
+        <v>0.3502454991816694</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>0.6292</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.0680952380952381</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>0.294018691588785</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>0.6292</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.0680952380952381</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0.294018691588785</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
       <c r="U4">
-        <v>1.87</v>
+        <v>3.82</v>
       </c>
       <c r="V4">
-        <v>0.2586445366528354</v>
+        <v>0.4134199134199134</v>
       </c>
       <c r="W4">
-        <v>0.58656330749354</v>
+        <v>0.3513957307060755</v>
       </c>
       <c r="X4">
-        <v>0.1405311141478158</v>
+        <v>0.1088190984918132</v>
       </c>
       <c r="Y4">
-        <v>0.4460321933457242</v>
+        <v>0.2425766322142624</v>
       </c>
       <c r="Z4">
-        <v>0.3911262798634813</v>
+        <v>0.2207369942196532</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.05908847209848473</v>
+        <v>0.04971110596713295</v>
       </c>
       <c r="AC4">
-        <v>-0.05908847209848473</v>
+        <v>-0.04971110596713295</v>
       </c>
       <c r="AD4">
-        <v>28.6</v>
+        <v>38.7</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>28.6</v>
+        <v>38.7</v>
       </c>
       <c r="AG4">
-        <v>26.73</v>
+        <v>34.88</v>
       </c>
       <c r="AH4">
-        <v>0.7982137873290539</v>
+        <v>0.8072590738423029</v>
       </c>
       <c r="AI4">
-        <v>0.8244450850389162</v>
+        <v>0.7771084337349398</v>
       </c>
       <c r="AJ4">
-        <v>0.7871024734982333</v>
+        <v>0.7905711695376246</v>
       </c>
       <c r="AK4">
-        <v>0.8144424131627057</v>
+        <v>0.7585906916050457</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -963,7 +972,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sequoia Financial Group Limited (ASX:SEQ)</t>
+          <t>E&amp;P Financial Group Limited (ASX:EP1)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -972,10 +981,7 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.446</v>
-      </c>
-      <c r="E5">
-        <v>0.524</v>
+        <v>-0.106</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -990,94 +996,91 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>4.73</v>
+        <v>-11.3</v>
       </c>
       <c r="L5">
-        <v>0.05320584926884139</v>
+        <v>-0.09792027729636049</v>
       </c>
       <c r="M5">
-        <v>0.757</v>
+        <v>4.339</v>
       </c>
       <c r="N5">
-        <v>0.01399260628465804</v>
+        <v>0.05527388535031846</v>
       </c>
       <c r="O5">
-        <v>0.1600422832980972</v>
+        <v>-0.3839823008849557</v>
       </c>
       <c r="P5">
-        <v>0.757</v>
+        <v>4.27</v>
       </c>
       <c r="Q5">
-        <v>0.01399260628465804</v>
+        <v>0.05439490445859872</v>
       </c>
       <c r="R5">
-        <v>0.1600422832980972</v>
+        <v>-0.3778761061946902</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>0.06899999999999995</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>0.01590228163171237</v>
       </c>
       <c r="U5">
-        <v>26</v>
+        <v>35.5</v>
       </c>
       <c r="V5">
-        <v>0.4805914972273567</v>
+        <v>0.4522292993630573</v>
       </c>
       <c r="W5">
-        <v>0.1707581227436823</v>
+        <v>-0.1003552397868561</v>
       </c>
       <c r="X5">
-        <v>0.07137928191446533</v>
+        <v>0.05983197285311616</v>
       </c>
       <c r="Y5">
-        <v>0.099378840829217</v>
+        <v>-0.1601872126399723</v>
       </c>
       <c r="Z5">
-        <v>3.445736434108528</v>
+        <v>2</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.06264449574283272</v>
+        <v>0.05523669948349816</v>
       </c>
       <c r="AC5">
-        <v>-0.06264449574283272</v>
+        <v>-0.05523669948349816</v>
       </c>
       <c r="AD5">
-        <v>16</v>
+        <v>20.3</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>16</v>
+        <v>20.3</v>
       </c>
       <c r="AG5">
-        <v>-10</v>
+        <v>-15.2</v>
       </c>
       <c r="AH5">
-        <v>0.2282453637660485</v>
+        <v>0.2054655870445344</v>
       </c>
       <c r="AI5">
-        <v>0.3361344537815126</v>
+        <v>0.1786971830985916</v>
       </c>
       <c r="AJ5">
-        <v>-0.2267573696145125</v>
+        <v>-0.2401263823064771</v>
       </c>
       <c r="AK5">
-        <v>-0.4629629629629629</v>
+        <v>-0.1946222791293214</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>-0.005</v>
-      </c>
-      <c r="AQ5">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -1088,7 +1091,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>E&amp;P Financial Group Limited (ASX:EP1)</t>
+          <t>HUB24 Limited (ASX:HUB)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1097,10 +1100,13 @@
         </is>
       </c>
       <c r="D6">
-        <v>-0.0134</v>
+        <v>0.268</v>
       </c>
       <c r="E6">
-        <v>-0.187</v>
+        <v>0.389</v>
+      </c>
+      <c r="F6">
+        <v>0.179</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1115,85 +1121,85 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>4.35</v>
+        <v>25.4</v>
       </c>
       <c r="L6">
-        <v>0.03082919914953933</v>
+        <v>0.1374458874458874</v>
       </c>
       <c r="M6">
-        <v>7.094999999999999</v>
+        <v>20.76</v>
       </c>
       <c r="N6">
-        <v>0.08969658659924146</v>
+        <v>0.01046476459320496</v>
       </c>
       <c r="O6">
-        <v>1.631034482758621</v>
+        <v>0.8173228346456692</v>
       </c>
       <c r="P6">
-        <v>4.274999999999999</v>
+        <v>14.1</v>
       </c>
       <c r="Q6">
-        <v>0.05404551201011377</v>
+        <v>0.007107571327754814</v>
       </c>
       <c r="R6">
-        <v>0.9827586206896551</v>
+        <v>0.5551181102362205</v>
       </c>
       <c r="S6">
-        <v>2.819999999999999</v>
+        <v>6.659999999999998</v>
       </c>
       <c r="T6">
-        <v>0.3974630021141649</v>
+        <v>0.3208092485549133</v>
       </c>
       <c r="U6">
-        <v>51.1</v>
+        <v>48.4</v>
       </c>
       <c r="V6">
-        <v>0.6460176991150444</v>
+        <v>0.02439762072789596</v>
       </c>
       <c r="W6">
-        <v>0.036770921386306</v>
+        <v>0.08091748964638421</v>
       </c>
       <c r="X6">
-        <v>0.0756086412957668</v>
+        <v>0.05677610343117495</v>
       </c>
       <c r="Y6">
-        <v>-0.0388377199094608</v>
+        <v>0.02414138621520925</v>
       </c>
       <c r="Z6">
-        <v>2.528673835125448</v>
+        <v>1.117291414752116</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.06382961336518431</v>
+        <v>0.05649485895884847</v>
       </c>
       <c r="AC6">
-        <v>-0.06382961336518431</v>
+        <v>-0.05649485895884847</v>
       </c>
       <c r="AD6">
-        <v>41.1</v>
+        <v>26.7</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>41.1</v>
+        <v>26.7</v>
       </c>
       <c r="AG6">
-        <v>-10</v>
+        <v>-21.7</v>
       </c>
       <c r="AH6">
-        <v>0.3419301164725458</v>
+        <v>0.01328027853767719</v>
       </c>
       <c r="AI6">
-        <v>0.2674040338321406</v>
+        <v>0.07287117903930131</v>
       </c>
       <c r="AJ6">
-        <v>-0.1447178002894356</v>
+        <v>-0.01105957902247592</v>
       </c>
       <c r="AK6">
-        <v>-0.09746588693957116</v>
+        <v>-0.06823899371069182</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1210,7 +1216,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BIR Financial Limited (ASX:BIR)</t>
+          <t>SelfWealth Limited (ASX:SWF)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1219,10 +1225,10 @@
         </is>
       </c>
       <c r="D7">
-        <v>1.393</v>
+        <v>0.9590000000000001</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>0.02820512820512821</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -1234,10 +1240,10 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>-2.14</v>
+        <v>0.061</v>
       </c>
       <c r="L7">
-        <v>-1.086294416243655</v>
+        <v>0.003128205128205128</v>
       </c>
       <c r="M7">
         <v>-0</v>
@@ -1246,7 +1252,7 @@
         <v>-0</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P7">
         <v>-0</v>
@@ -1255,67 +1261,70 @@
         <v>-0</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
       <c r="U7">
-        <v>0.048</v>
+        <v>8.25</v>
       </c>
       <c r="V7">
-        <v>0.006611570247933885</v>
+        <v>0.3101503759398496</v>
       </c>
       <c r="W7">
-        <v>1.289156626506024</v>
+        <v>0.008036890645586298</v>
       </c>
       <c r="X7">
-        <v>0.07026767278572359</v>
+        <v>0.05675547863448045</v>
       </c>
       <c r="Y7">
-        <v>1.2188889537203</v>
+        <v>-0.04871858798889415</v>
       </c>
       <c r="Z7">
-        <v>5.02551020408163</v>
+        <v>96.0591133004929</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.06469248378890348</v>
+        <v>0.05650864459675931</v>
       </c>
       <c r="AC7">
-        <v>-0.06469248378890348</v>
+        <v>-0.05650864459675931</v>
       </c>
       <c r="AD7">
-        <v>1.72</v>
+        <v>0.314</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>1.72</v>
+        <v>0.314</v>
       </c>
       <c r="AG7">
-        <v>1.672</v>
+        <v>-7.936</v>
       </c>
       <c r="AH7">
-        <v>0.1915367483296214</v>
+        <v>0.01166679051794605</v>
       </c>
       <c r="AI7">
-        <v>-4.410256410256411</v>
+        <v>0.04081102157525344</v>
       </c>
       <c r="AJ7">
-        <v>0.187192118226601</v>
+        <v>-0.4252036005143592</v>
       </c>
       <c r="AK7">
-        <v>-3.817351598173516</v>
+        <v>14.27338129496403</v>
       </c>
       <c r="AL7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>0</v>
+        <v>-0.171</v>
+      </c>
+      <c r="AQ7">
+        <v>-0</v>
       </c>
     </row>
     <row r="8">
@@ -1326,7 +1335,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Euroz Hartleys Group Limited (ASX:EZL)</t>
+          <t>Halo Technologies Holdings Limited (ASX:HAL)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1334,14 +1343,8 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D8">
-        <v>0.17</v>
-      </c>
-      <c r="E8">
-        <v>0.16</v>
-      </c>
       <c r="G8">
-        <v>0</v>
+        <v>0.0616710875331565</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -1353,85 +1356,82 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>28.1</v>
+        <v>-3.32</v>
       </c>
       <c r="L8">
-        <v>0.3435207823960881</v>
+        <v>-0.4403183023872679</v>
       </c>
       <c r="M8">
-        <v>23.49</v>
+        <v>-0</v>
       </c>
       <c r="N8">
-        <v>0.1967336683417085</v>
+        <v>-0</v>
       </c>
       <c r="O8">
-        <v>0.8359430604982205</v>
+        <v>0</v>
       </c>
       <c r="P8">
-        <v>21.5</v>
+        <v>-0</v>
       </c>
       <c r="Q8">
-        <v>0.1800670016750419</v>
+        <v>-0</v>
       </c>
       <c r="R8">
-        <v>0.7651245551601423</v>
+        <v>0</v>
       </c>
       <c r="S8">
-        <v>1.989999999999998</v>
-      </c>
-      <c r="T8">
-        <v>0.08471690080885477</v>
+        <v>0</v>
       </c>
       <c r="U8">
-        <v>131.4</v>
+        <v>8.99</v>
       </c>
       <c r="V8">
-        <v>1.100502512562814</v>
+        <v>0.5226744186046512</v>
       </c>
       <c r="W8">
-        <v>0.2190179267342167</v>
+        <v>-0.1824175824175824</v>
       </c>
       <c r="X8">
-        <v>0.06632626613547396</v>
+        <v>0.0566083256279756</v>
       </c>
       <c r="Y8">
-        <v>0.1526916605987427</v>
+        <v>-0.239025908045558</v>
       </c>
       <c r="Z8">
-        <v>1.671434409480997</v>
+        <v>1.47843137254902</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.065560239261896</v>
+        <v>0.0566083256279756</v>
       </c>
       <c r="AC8">
-        <v>-0.065560239261896</v>
+        <v>-0.0566083256279756</v>
       </c>
       <c r="AD8">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="AG8">
-        <v>-128.02</v>
+        <v>-8.99</v>
       </c>
       <c r="AH8">
-        <v>0.02752891350382798</v>
+        <v>0</v>
       </c>
       <c r="AI8">
-        <v>0.02476553341148886</v>
+        <v>0</v>
       </c>
       <c r="AJ8">
-        <v>14.85150812064965</v>
+        <v>-1.095006090133983</v>
       </c>
       <c r="AK8">
-        <v>-25.20078740157489</v>
+        <v>-1.693032015065913</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1448,7 +1448,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>HUB24 Limited (ASX:HUB)</t>
+          <t>Raiz Invest Limited (ASX:RZI)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1457,106 +1457,97 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.25</v>
-      </c>
-      <c r="E9">
-        <v>-0.0493</v>
-      </c>
-      <c r="F9">
-        <v>0.267</v>
+        <v>0.473</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>-0.40859375</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>-0.40859375</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>-0.41171875</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>-0.41171875</v>
       </c>
       <c r="K9">
-        <v>10.1</v>
+        <v>-4.59</v>
       </c>
       <c r="L9">
-        <v>0.07645722937168811</v>
+        <v>-0.35859375</v>
       </c>
       <c r="M9">
-        <v>13.63</v>
+        <v>-0</v>
       </c>
       <c r="N9">
-        <v>0.009457396613932833</v>
+        <v>-0</v>
       </c>
       <c r="O9">
-        <v>1.34950495049505</v>
+        <v>0</v>
       </c>
       <c r="P9">
-        <v>6.73</v>
+        <v>-0</v>
       </c>
       <c r="Q9">
-        <v>0.004669719678046073</v>
+        <v>-0</v>
       </c>
       <c r="R9">
-        <v>0.6663366336633664</v>
+        <v>0</v>
       </c>
       <c r="S9">
-        <v>6.9</v>
-      </c>
-      <c r="T9">
-        <v>0.5062362435803375</v>
+        <v>0</v>
       </c>
       <c r="U9">
-        <v>29.9</v>
+        <v>5.62</v>
       </c>
       <c r="V9">
-        <v>0.0207466000555093</v>
+        <v>0.2203921568627451</v>
       </c>
       <c r="W9">
-        <v>0.07437407952871869</v>
+        <v>-0.1390909090909091</v>
       </c>
       <c r="X9">
-        <v>0.06623845879236283</v>
+        <v>0.05681560057097103</v>
       </c>
       <c r="Y9">
-        <v>0.008135620736355861</v>
+        <v>-0.1959065096618801</v>
       </c>
       <c r="Z9">
-        <v>2.410583941605838</v>
+        <v>1.484057971014493</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>-0.6110144927536233</v>
       </c>
       <c r="AB9">
-        <v>0.06559731363895703</v>
+        <v>0.05646858426785069</v>
       </c>
       <c r="AC9">
-        <v>-0.06559731363895703</v>
+        <v>-0.667483077021474</v>
       </c>
       <c r="AD9">
-        <v>34.1</v>
+        <v>0.424</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>34.1</v>
+        <v>0.424</v>
       </c>
       <c r="AG9">
-        <v>4.200000000000003</v>
+        <v>-5.196</v>
       </c>
       <c r="AH9">
-        <v>0.02311394292686234</v>
+        <v>0.01635550069433729</v>
       </c>
       <c r="AI9">
-        <v>0.09798850574712645</v>
+        <v>0.01623028632674935</v>
       </c>
       <c r="AJ9">
-        <v>0.002905770029057702</v>
+        <v>-0.2559101654846335</v>
       </c>
       <c r="AK9">
-        <v>0.01320339515875512</v>
+        <v>-0.2534139680062427</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1564,127 +1555,11 @@
       <c r="AM9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Raiz Invest Limited (ASX:RZI)</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Brokerage &amp; Investment Banking</t>
-        </is>
-      </c>
-      <c r="D10">
-        <v>0.188</v>
-      </c>
-      <c r="G10">
-        <v>-0.5676691729323308</v>
-      </c>
-      <c r="H10">
-        <v>-0.5676691729323308</v>
-      </c>
-      <c r="I10">
-        <v>-0.5699248120300752</v>
-      </c>
-      <c r="J10">
-        <v>-0.5699248120300752</v>
-      </c>
-      <c r="K10">
-        <v>-6.64</v>
-      </c>
-      <c r="L10">
-        <v>-0.4992481203007518</v>
-      </c>
-      <c r="M10">
-        <v>-0</v>
-      </c>
-      <c r="N10">
-        <v>-0</v>
-      </c>
-      <c r="O10">
-        <v>0</v>
-      </c>
-      <c r="P10">
-        <v>-0</v>
-      </c>
-      <c r="Q10">
-        <v>-0</v>
-      </c>
-      <c r="R10">
-        <v>0</v>
-      </c>
-      <c r="S10">
-        <v>0</v>
-      </c>
-      <c r="U10">
-        <v>10.7</v>
-      </c>
-      <c r="V10">
-        <v>0.4115384615384615</v>
-      </c>
-      <c r="W10">
-        <v>-0.2313588850174216</v>
-      </c>
-      <c r="X10">
-        <v>0.06646360115533642</v>
-      </c>
-      <c r="Y10">
-        <v>-0.297822486172758</v>
-      </c>
-      <c r="Z10">
-        <v>3.002935199819373</v>
-      </c>
-      <c r="AA10">
-        <v>-1.711447279295553</v>
-      </c>
-      <c r="AB10">
-        <v>0.0655029203357009</v>
-      </c>
-      <c r="AC10">
-        <v>-1.776950199631254</v>
-      </c>
-      <c r="AD10">
-        <v>0.925</v>
-      </c>
-      <c r="AE10">
-        <v>0</v>
-      </c>
-      <c r="AF10">
-        <v>0.925</v>
-      </c>
-      <c r="AG10">
-        <v>-9.774999999999999</v>
-      </c>
-      <c r="AH10">
-        <v>0.03435468895078923</v>
-      </c>
-      <c r="AI10">
-        <v>0.02835249042145594</v>
-      </c>
-      <c r="AJ10">
-        <v>-0.6024653312788905</v>
-      </c>
-      <c r="AK10">
-        <v>-0.4458380843785632</v>
-      </c>
-      <c r="AL10">
-        <v>0</v>
-      </c>
-      <c r="AM10">
-        <v>0</v>
-      </c>
-      <c r="AN10">
-        <v>-0.1225165562913907</v>
-      </c>
-      <c r="AP10">
-        <v>1.294701986754967</v>
+      <c r="AN9">
+        <v>-0.08107074569789674</v>
+      </c>
+      <c r="AP9">
+        <v>0.9934990439770554</v>
       </c>
     </row>
   </sheetData>
